--- a/Model/PROP_RANKINGS.xlsx
+++ b/Model/PROP_RANKINGS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\MLB\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DED07D-E903-4F10-8BAC-6114CEC8902E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C668BE-7D40-448E-9911-1153DC20C01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Pitching Props 'xK' + 'K &gt; x': starter strikeouts O/U</t>
+    <t>Pitcher xK + K &gt; x</t>
   </si>
   <si>
     <t>k</t>
@@ -74,7 +74,7 @@
     <t>unbiased; tails priced right</t>
   </si>
   <si>
-    <t>Pitching Props 'xOuts' + 'Outs &gt; x': starter outs O/U</t>
+    <t>Pitcher xOuts + Outs &gt; x</t>
   </si>
   <si>
     <t>outs</t>
@@ -83,7 +83,7 @@
     <t>over-predicts +0.14 -&gt; lean unders; tails priced right</t>
   </si>
   <si>
-    <t>Batter Props 'SB': 1+ stolen base</t>
+    <t>Batter SB</t>
   </si>
   <si>
     <t>sb</t>
@@ -92,7 +92,7 @@
     <t>calibrated -&gt; price bets directly; top picks 3.1x base -&gt; follow the list deep</t>
   </si>
   <si>
-    <t>Pitching Props 'xBB' + 'BB &gt; x': walks allowed O/U</t>
+    <t>Pitcher xBB + BB &gt; x</t>
   </si>
   <si>
     <t>pbb</t>
@@ -101,7 +101,7 @@
     <t>2 STRONG</t>
   </si>
   <si>
-    <t>Batter Props 'xSO': expected batter strikeouts</t>
+    <t>Batter xSO</t>
   </si>
   <si>
     <t>xbk</t>
@@ -110,7 +110,7 @@
     <t>unbiased; tails priced right; half-point lines overlap the binary columns</t>
   </si>
   <si>
-    <t>Batter Props 'HR': 1+ home run</t>
+    <t>Batter HR</t>
   </si>
   <si>
     <t>hr</t>
@@ -119,7 +119,7 @@
     <t>calibrated -&gt; price bets directly; top picks 2.1x base -&gt; follow the list deep</t>
   </si>
   <si>
-    <t>Batter Props '2+ K': 2+ strikeouts by the batter</t>
+    <t>Batter 2+ K</t>
   </si>
   <si>
     <t>bk2</t>
@@ -128,7 +128,7 @@
     <t>top picks 1.9x -&gt; top 3-10 only</t>
   </si>
   <si>
-    <t>Pitching Props 'xHits' + 'Hits &gt; x': hits allowed O/U</t>
+    <t>Pitcher xHits + Hits &gt; x</t>
   </si>
   <si>
     <t>pha</t>
@@ -140,7 +140,7 @@
     <t>over-predicts +0.16 -&gt; lean unders; tails priced right</t>
   </si>
   <si>
-    <t>Batter Props 'K': 1+ strikeout by the batter</t>
+    <t>Batter K</t>
   </si>
   <si>
     <t>bk</t>
@@ -149,7 +149,7 @@
     <t>picks only 1.3x base -&gt; no selection power</t>
   </si>
   <si>
-    <t>Batter Props 'BB': 1+ walk</t>
+    <t>Batter BB</t>
   </si>
   <si>
     <t>bb</t>
@@ -158,7 +158,7 @@
     <t>probability level drifts (ECE 0.011) -&gt; trust picks more than prices; top picks 1.7x -&gt; top 3-10 only</t>
   </si>
   <si>
-    <t>Batter Props '2+ Hits'</t>
+    <t>Batter 2+ Hits</t>
   </si>
   <si>
     <t>hits2</t>
@@ -170,7 +170,7 @@
     <t>calibrated -&gt; price bets directly; top picks 1.5x -&gt; top 3-10 only</t>
   </si>
   <si>
-    <t>Batter Props 'H+R+RBI 3+'</t>
+    <t>Batter H+R+RBI 3+</t>
   </si>
   <si>
     <t>hrr3</t>
@@ -179,7 +179,7 @@
     <t>top picks 1.5x -&gt; top 3-10 only</t>
   </si>
   <si>
-    <t>Pitching Props 'xER' + 'ER &gt; x': earned runs O/U</t>
+    <t>Pitcher xER + ER &gt; x</t>
   </si>
   <si>
     <t>per</t>
@@ -188,7 +188,7 @@
     <t>unbiased; wild tails (disp 1.6) -&gt; shade extreme lines</t>
   </si>
   <si>
-    <t>Batter Props '2+ TB': 2+ total bases</t>
+    <t>Batter 2+ TB</t>
   </si>
   <si>
     <t>tb2</t>
@@ -197,13 +197,13 @@
     <t>calibrated -&gt; price bets directly; picks only 1.4x base -&gt; no selection power</t>
   </si>
   <si>
-    <t>Batter Props 'H+R+RBI 2+'</t>
+    <t>Batter H+R+RBI 2+</t>
   </si>
   <si>
     <t>hrr2</t>
   </si>
   <si>
-    <t>Batter Props 'Run': scores a run</t>
+    <t>Batter Run</t>
   </si>
   <si>
     <t>run</t>
@@ -212,7 +212,7 @@
     <t>picks only 1.4x base -&gt; no selection power</t>
   </si>
   <si>
-    <t>Batter Props 'RBI': 1+ run batted in</t>
+    <t>Batter RBI</t>
   </si>
   <si>
     <t>rbi</t>
@@ -221,7 +221,7 @@
     <t>5 AVOID</t>
   </si>
   <si>
-    <t>Batter Props 'Hit': 1+ hit</t>
+    <t>Batter Hit</t>
   </si>
   <si>
     <t>hit</t>
@@ -230,7 +230,7 @@
     <t>calibrated -&gt; price bets directly; picks only 1.2x base -&gt; no selection power</t>
   </si>
   <si>
-    <t>Batter Props 'Single': 1+ single</t>
+    <t>Batter Single</t>
   </si>
   <si>
     <t>single</t>
@@ -239,7 +239,7 @@
     <t>calibrated -&gt; price bets directly; picks only 1.3x base -&gt; no selection power</t>
   </si>
   <si>
-    <t>Batter Props 'xHRR': expected hits+runs+RBIs</t>
+    <t>Batter xHRR</t>
   </si>
   <si>
     <t>xhrr</t>
@@ -248,13 +248,13 @@
     <t>unbiased; wild tails (disp 2.0) -&gt; shade extreme lines; half-point lines overlap the binary columns</t>
   </si>
   <si>
-    <t>Batter Props 'xTB': expected total bases</t>
+    <t>Batter xTB</t>
   </si>
   <si>
     <t>xtb</t>
   </si>
   <si>
-    <t>Games 'Total Runs' + 'Runs &gt; x': game total O/U</t>
+    <t>Game Total Runs + Runs &gt; x</t>
   </si>
   <si>
     <t>total</t>
@@ -263,7 +263,7 @@
     <t>unbiased; wild tails (disp 2.3) -&gt; shade extreme lines</t>
   </si>
   <si>
-    <t>Batter Props 'Double': 1+ double</t>
+    <t>Batter Double</t>
   </si>
   <si>
     <t>double</t>
@@ -330,7 +330,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +345,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF0F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -375,17 +405,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -393,6 +414,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -700,18 +739,15 @@
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="89" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="4" customWidth="1"/>
+    <col min="2" max="2" width="41" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7" style="4" customWidth="1"/>
+    <col min="6" max="7" width="6" style="4" customWidth="1"/>
+    <col min="8" max="12" width="8" style="4" customWidth="1"/>
+    <col min="13" max="13" width="90" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -759,7 +795,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -796,7 +832,7 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -823,7 +859,7 @@
         <v>0.82</v>
       </c>
       <c r="L3" s="3">
-        <v>10.09</v>
+        <v>10.07</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>19</v>
@@ -833,7 +869,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -870,7 +906,7 @@
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -907,7 +943,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -944,7 +980,7 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -981,7 +1017,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1018,7 +1054,7 @@
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1055,7 +1091,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1092,7 +1128,7 @@
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1129,7 +1165,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1166,7 +1202,7 @@
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1203,7 +1239,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1230,7 +1266,7 @@
         <v>1.57</v>
       </c>
       <c r="L14" s="2">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>54</v>
@@ -1240,7 +1276,7 @@
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1277,7 +1313,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1314,7 +1350,7 @@
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1351,7 +1387,7 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1388,7 +1424,7 @@
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1425,7 +1461,7 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1462,7 +1498,7 @@
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1499,7 +1535,7 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1536,7 +1572,7 @@
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1573,7 +1609,7 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1610,7 +1646,7 @@
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="9" t="s">
         <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1648,74 +1684,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>95</v>
       </c>
     </row>
